--- a/cet4/result/09_舞台女王_重生影后的逆袭/09_舞台女王_重生影后的逆袭_学习版.xlsx
+++ b/cet4/result/09_舞台女王_重生影后的逆袭/09_舞台女王_重生影后的逆袭_学习版.xlsx
@@ -397,927 +397,829 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D58"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>college</v>
       </c>
       <c r="B2" t="str">
-        <v>college</v>
+        <v>/ˈkɑːlɪdʒ/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>学院</v>
       </c>
-      <c r="D2" t="str">
-        <v>college(学院)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>major</v>
       </c>
       <c r="B3" t="str">
-        <v>major</v>
+        <v>/ˈmeɪdʒər/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./vi./adj.</v>
+      </c>
+      <c r="D3" t="str">
         <v>主修</v>
       </c>
-      <c r="D3" t="str">
-        <v>major(主修)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>theatre</v>
       </c>
       <c r="B4" t="str">
-        <v>theatre</v>
+        <v>/ˈθiːətər/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>剧院</v>
       </c>
-      <c r="D4" t="str">
-        <v>theatre(剧院)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>bag</v>
       </c>
       <c r="B5" t="str">
-        <v>bag</v>
+        <v>/bæɡ/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D5" t="str">
         <v>包</v>
       </c>
-      <c r="D5" t="str">
-        <v>bag(包)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>forth</v>
       </c>
       <c r="B6" t="str">
-        <v>forth</v>
+        <v>/fɔːrθ/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./v./adv.</v>
+      </c>
+      <c r="D6" t="str">
         <v>向前</v>
       </c>
-      <c r="D6" t="str">
-        <v>forth(向前)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>hillside</v>
       </c>
       <c r="B7" t="str">
-        <v>hillside</v>
+        <v>/ˈhɪlsaɪd/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>山坡</v>
       </c>
-      <c r="D7" t="str">
-        <v>hillside(山坡)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>step</v>
       </c>
       <c r="B8" t="str">
-        <v>step</v>
+        <v>/step/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D8" t="str">
         <v>步</v>
       </c>
-      <c r="D8" t="str">
-        <v>step(步)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>landlady</v>
       </c>
       <c r="B9" t="str">
-        <v>landlady</v>
+        <v>/ˈlændleɪdi/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>女房东</v>
       </c>
-      <c r="D9" t="str">
-        <v>landlady(女房东)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>biscuit</v>
       </c>
       <c r="B10" t="str">
-        <v>biscuit</v>
+        <v>/ˈbɪskɪt/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>饼干</v>
       </c>
-      <c r="D10" t="str">
-        <v>biscuit(饼干)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>bread</v>
       </c>
       <c r="B11" t="str">
-        <v>bread</v>
+        <v>/bred/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D11" t="str">
         <v>面包</v>
       </c>
-      <c r="D11" t="str">
-        <v>bread(面包)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>secret</v>
       </c>
       <c r="B12" t="str">
-        <v>secret</v>
+        <v>/ˈsiːkrət/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>秘密</v>
       </c>
-      <c r="D12" t="str">
-        <v>secret(秘密)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>absolute</v>
       </c>
       <c r="B13" t="str">
-        <v>absolute</v>
+        <v>/ˈæbsəluːt/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D13" t="str">
         <v>绝对的</v>
       </c>
-      <c r="D13" t="str">
-        <v>absolute(绝对的)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>inevitable</v>
       </c>
       <c r="B14" t="str">
-        <v>inevitable</v>
+        <v>/ɪnˈevɪtəbl/</v>
       </c>
       <c r="C14" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>不可避免的</v>
       </c>
-      <c r="D14" t="str">
-        <v>inevitable(不可避免的)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>version</v>
       </c>
       <c r="B15" t="str">
-        <v>version</v>
+        <v>/ˈvɜːrʒn/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>版本</v>
       </c>
-      <c r="D15" t="str">
-        <v>version(版本)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>intellectual</v>
       </c>
       <c r="B16" t="str">
-        <v>intellectual</v>
+        <v>/ˌɪntəˈlektʃuəl/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D16" t="str">
         <v>知识分子</v>
       </c>
-      <c r="D16" t="str">
-        <v>intellectual(知识分子)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>picture</v>
       </c>
       <c r="B17" t="str">
-        <v>picture</v>
+        <v>/ˈpɪktʃər/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D17" t="str">
         <v>照片</v>
       </c>
-      <c r="D17" t="str">
-        <v>picture(照片)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>evaluate</v>
       </c>
       <c r="B18" t="str">
-        <v>evaluate</v>
+        <v>/ɪˈvæljueɪt/</v>
       </c>
       <c r="C18" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D18" t="str">
         <v>评价</v>
       </c>
-      <c r="D18" t="str">
-        <v>evaluate(评价)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>cupboard</v>
       </c>
       <c r="B19" t="str">
-        <v>cupboard</v>
+        <v>/ˈkʌbərd/</v>
       </c>
       <c r="C19" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>碗柜</v>
       </c>
-      <c r="D19" t="str">
-        <v>cupboard(碗柜)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>lemon</v>
       </c>
       <c r="B20" t="str">
-        <v>lemon</v>
+        <v>/ˈlemən/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D20" t="str">
         <v>柠檬</v>
       </c>
-      <c r="D20" t="str">
-        <v>lemon(柠檬)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>hammer</v>
       </c>
       <c r="B21" t="str">
-        <v>hammer</v>
+        <v>/ˈhæmər/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D21" t="str">
         <v>锤子</v>
       </c>
-      <c r="D21" t="str">
-        <v>hammer(锤子)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>lump</v>
       </c>
       <c r="B22" t="str">
-        <v>lump</v>
+        <v>/lʌmp/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./vt./vi./v./adj./adv.</v>
+      </c>
+      <c r="D22" t="str">
         <v>块状物</v>
       </c>
-      <c r="D22" t="str">
-        <v>lump(块状物)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>defect</v>
       </c>
       <c r="B23" t="str">
-        <v>defect</v>
+        <v>/'diːfekt/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D23" t="str">
         <v>缺陷</v>
       </c>
-      <c r="D23" t="str">
-        <v>defect(缺陷)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>could</v>
       </c>
       <c r="B24" t="str">
-        <v>could</v>
+        <v>/kəd,kʊd/</v>
       </c>
       <c r="C24" t="str">
+        <v>v./aux.</v>
+      </c>
+      <c r="D24" t="str">
         <v>能够</v>
       </c>
-      <c r="D24" t="str">
-        <v>could(能够)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>country</v>
       </c>
       <c r="B25" t="str">
-        <v>country</v>
+        <v>/ˈkʌntri/</v>
       </c>
       <c r="C25" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D25" t="str">
         <v>国家</v>
       </c>
-      <c r="D25" t="str">
-        <v>country(国家)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>darling</v>
       </c>
       <c r="B26" t="str">
-        <v>darling</v>
+        <v>/ˈdɑːrlɪŋ/</v>
       </c>
       <c r="C26" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>亲爱的</v>
       </c>
-      <c r="D26" t="str">
-        <v>darling(亲爱的)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>adult</v>
       </c>
       <c r="B27" t="str">
-        <v>adult</v>
+        <v>/əˈdʌlt,ˈædʌlt/</v>
       </c>
       <c r="C27" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D27" t="str">
         <v>成年人</v>
       </c>
-      <c r="D27" t="str">
-        <v>adult(成年人)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>generous</v>
       </c>
       <c r="B28" t="str">
-        <v>generous</v>
+        <v>/ˈdʒenərəs/</v>
       </c>
       <c r="C28" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D28" t="str">
         <v>慷慨的</v>
       </c>
-      <c r="D28" t="str">
-        <v>generous(慷慨的)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>fundamental</v>
       </c>
       <c r="B29" t="str">
-        <v>fundamental</v>
+        <v>/ˌfʌndəˈmentl/</v>
       </c>
       <c r="C29" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D29" t="str">
         <v>根本的</v>
       </c>
-      <c r="D29" t="str">
-        <v>fundamental(根本的)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>radiation</v>
       </c>
       <c r="B30" t="str">
-        <v>radiation</v>
+        <v>/ˌreɪdiˈeɪʃn/</v>
       </c>
       <c r="C30" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>辐射</v>
       </c>
-      <c r="D30" t="str">
-        <v>radiation(辐射)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>some</v>
       </c>
       <c r="B31" t="str">
-        <v>some</v>
+        <v>/səm,sʌm/</v>
       </c>
       <c r="C31" t="str">
+        <v>n./adj./pron.</v>
+      </c>
+      <c r="D31" t="str">
         <v>一些</v>
       </c>
-      <c r="D31" t="str">
-        <v>some(一些)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>almost</v>
       </c>
       <c r="B32" t="str">
-        <v>almost</v>
+        <v>/ˈɔːlmoʊst/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D32" t="str">
         <v>几乎</v>
       </c>
-      <c r="D32" t="str">
-        <v>almost(几乎)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>assign</v>
       </c>
       <c r="B33" t="str">
-        <v>assign</v>
+        <v>/əˈsaɪn/</v>
       </c>
       <c r="C33" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D33" t="str">
         <v>分配</v>
       </c>
-      <c r="D33" t="str">
-        <v>assign(分配)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>commercial</v>
       </c>
       <c r="B34" t="str">
-        <v>commercial</v>
+        <v>/kəˈmɜːrʃl/</v>
       </c>
       <c r="C34" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D34" t="str">
         <v>商业的</v>
       </c>
-      <c r="D34" t="str">
-        <v>commercial(商业的)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>grocery</v>
       </c>
       <c r="B35" t="str">
-        <v>grocery</v>
+        <v>/ˈɡroʊsəri/</v>
       </c>
       <c r="C35" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>杂货店</v>
       </c>
-      <c r="D35" t="str">
-        <v>grocery(杂货店)📢</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>bare</v>
       </c>
       <c r="B36" t="str">
-        <v>bare</v>
+        <v>/ber/</v>
       </c>
       <c r="C36" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D36" t="str">
         <v>赤裸的</v>
       </c>
-      <c r="D36" t="str">
-        <v>bare(赤裸的)📢</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>rail</v>
       </c>
       <c r="B37" t="str">
-        <v>rail</v>
+        <v>/reɪl/</v>
       </c>
       <c r="C37" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D37" t="str">
         <v>铁轨</v>
       </c>
-      <c r="D37" t="str">
-        <v>rail(铁轨)📢</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>rule</v>
       </c>
       <c r="B38" t="str">
-        <v>could</v>
+        <v>/ruːl/</v>
       </c>
       <c r="C38" t="str">
-        <v>能够</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D38" t="str">
-        <v>could(能够)📢</v>
+        <v>规则</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>wrong</v>
       </c>
       <c r="B39" t="str">
-        <v>rule</v>
+        <v>/rɔːŋ/</v>
       </c>
       <c r="C39" t="str">
-        <v>规则</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D39" t="str">
-        <v>rule(规则)📢</v>
+        <v>错误的</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>oppose</v>
       </c>
       <c r="B40" t="str">
-        <v>wrong</v>
+        <v>/əˈpoʊz/</v>
       </c>
       <c r="C40" t="str">
-        <v>错误的</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D40" t="str">
-        <v>wrong(错误的)📢</v>
+        <v>反对</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>terror</v>
       </c>
       <c r="B41" t="str">
-        <v>oppose</v>
+        <v>/ˈterər/</v>
       </c>
       <c r="C41" t="str">
-        <v>反对</v>
+        <v>n.</v>
       </c>
       <c r="D41" t="str">
-        <v>oppose(反对)📢</v>
+        <v>恐惧</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>merry</v>
       </c>
       <c r="B42" t="str">
-        <v>terror</v>
+        <v>/ˈmeri/</v>
       </c>
       <c r="C42" t="str">
-        <v>恐惧</v>
+        <v>n./adj.</v>
       </c>
       <c r="D42" t="str">
-        <v>terror(恐惧)📢</v>
+        <v>愉快的</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>smoothly</v>
       </c>
       <c r="B43" t="str">
-        <v>merry</v>
+        <v>/ˈsmuːðli/</v>
       </c>
       <c r="C43" t="str">
-        <v>愉快的</v>
+        <v>v./adv.</v>
       </c>
       <c r="D43" t="str">
-        <v>merry(愉快的)📢</v>
+        <v>平稳地</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>inch</v>
       </c>
       <c r="B44" t="str">
-        <v>smoothly</v>
+        <v>/ɪntʃ/</v>
       </c>
       <c r="C44" t="str">
-        <v>平稳地</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D44" t="str">
-        <v>smoothly(平稳地)📢</v>
+        <v>英寸</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>interrupt</v>
       </c>
       <c r="B45" t="str">
-        <v>lump</v>
+        <v>/ˌɪntəˈrʌpt/</v>
       </c>
       <c r="C45" t="str">
-        <v>肿块</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D45" t="str">
-        <v>lump(肿块)📢</v>
+        <v>打断</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>purify</v>
       </c>
       <c r="B46" t="str">
-        <v>inch</v>
+        <v>/ˈpjʊrɪfaɪ/</v>
       </c>
       <c r="C46" t="str">
-        <v>英寸</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D46" t="str">
-        <v>inch(英寸)📢</v>
+        <v>净化</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>glorious</v>
       </c>
       <c r="B47" t="str">
-        <v>interrupt</v>
+        <v>/ˈɡlɔːriəs/</v>
       </c>
       <c r="C47" t="str">
-        <v>打断</v>
+        <v>adj.</v>
       </c>
       <c r="D47" t="str">
-        <v>interrupt(打断)📢</v>
+        <v>辉煌的</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>hut</v>
       </c>
       <c r="B48" t="str">
-        <v>purify</v>
+        <v>/hʌt/</v>
       </c>
       <c r="C48" t="str">
-        <v>净化</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D48" t="str">
-        <v>purify(净化)📢</v>
+        <v>小屋</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>mate</v>
       </c>
       <c r="B49" t="str">
-        <v>glorious</v>
+        <v>/meɪt/</v>
       </c>
       <c r="C49" t="str">
-        <v>辉煌的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D49" t="str">
-        <v>glorious(辉煌的)📢</v>
+        <v>伙伴</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>spacious</v>
       </c>
       <c r="B50" t="str">
-        <v>almost</v>
+        <v/>
       </c>
       <c r="C50" t="str">
-        <v>几乎</v>
+        <v/>
       </c>
       <c r="D50" t="str">
-        <v>almost(几乎)📢</v>
+        <v>宽敞的</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>sulphur</v>
       </c>
       <c r="B51" t="str">
-        <v>biscuit</v>
+        <v>/ˈsʌlfər/</v>
       </c>
       <c r="C51" t="str">
-        <v>饼干</v>
+        <v>n./vt.</v>
       </c>
       <c r="D51" t="str">
-        <v>biscuit(饼干)📢</v>
+        <v>硫磺</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>spark</v>
       </c>
       <c r="B52" t="str">
-        <v>hut</v>
+        <v>/spɑːrk/</v>
       </c>
       <c r="C52" t="str">
-        <v>小屋</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D52" t="str">
-        <v>hut(小屋)📢</v>
+        <v>火花</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53">
-        <v>52</v>
+      <c r="A53" t="str">
+        <v>respond</v>
       </c>
       <c r="B53" t="str">
-        <v>mate</v>
+        <v>/rɪˈspɑːnd/</v>
       </c>
       <c r="C53" t="str">
-        <v>伙伴</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D53" t="str">
-        <v>mate(伙伴)📢</v>
+        <v>回答</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54">
-        <v>53</v>
+      <c r="A54" t="str">
+        <v>insult</v>
       </c>
       <c r="B54" t="str">
-        <v>spacious</v>
+        <v>/ɪnˈsʌlt; ˈɪnsʌlt     /</v>
       </c>
       <c r="C54" t="str">
-        <v>宽敞的</v>
+        <v>n./v.</v>
       </c>
       <c r="D54" t="str">
-        <v>spacious(宽敞的)📢</v>
+        <v>侮辱</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55">
-        <v>54</v>
+      <c r="A55" t="str">
+        <v>happiness</v>
       </c>
       <c r="B55" t="str">
-        <v>sulphur</v>
+        <v>/ˈhæpinəs/</v>
       </c>
       <c r="C55" t="str">
-        <v>硫磺</v>
+        <v>n.</v>
       </c>
       <c r="D55" t="str">
-        <v>sulphur(硫磺)📢</v>
+        <v>幸福</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56">
-        <v>55</v>
+      <c r="A56" t="str">
+        <v>survey</v>
       </c>
       <c r="B56" t="str">
-        <v>spark</v>
+        <v>/ˈsɜːrveɪ/</v>
       </c>
       <c r="C56" t="str">
-        <v>火花</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D56" t="str">
-        <v>spark(火花)📢</v>
+        <v>调查</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57">
-        <v>56</v>
+      <c r="A57" t="str">
+        <v>removal</v>
       </c>
       <c r="B57" t="str">
-        <v>respond</v>
+        <v>/rɪˈmuːvl/</v>
       </c>
       <c r="C57" t="str">
-        <v>回答</v>
+        <v>n.</v>
       </c>
       <c r="D57" t="str">
-        <v>respond(回答)📢</v>
+        <v>搬迁</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58">
-        <v>57</v>
+      <c r="A58" t="str">
+        <v>journey</v>
       </c>
       <c r="B58" t="str">
-        <v>insult</v>
+        <v>/ˈdʒɜːrni/</v>
       </c>
       <c r="C58" t="str">
-        <v>侮辱</v>
+        <v>n./vi.</v>
       </c>
       <c r="D58" t="str">
-        <v>insult(侮辱)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>happiness</v>
-      </c>
-      <c r="C59" t="str">
-        <v>幸福</v>
-      </c>
-      <c r="D59" t="str">
-        <v>happiness(幸福)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>survey</v>
-      </c>
-      <c r="C60" t="str">
-        <v>调查</v>
-      </c>
-      <c r="D60" t="str">
-        <v>survey(调查)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>major</v>
-      </c>
-      <c r="C61" t="str">
-        <v>重大的</v>
-      </c>
-      <c r="D61" t="str">
-        <v>major(重大的)📢</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>removal</v>
-      </c>
-      <c r="C62" t="str">
-        <v>搬迁</v>
-      </c>
-      <c r="D62" t="str">
-        <v>removal(搬迁)📢</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
-        <v>country</v>
-      </c>
-      <c r="C63" t="str">
-        <v>国家</v>
-      </c>
-      <c r="D63" t="str">
-        <v>country(国家)📢</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
-        <v>biscuit</v>
-      </c>
-      <c r="C64" t="str">
-        <v>饼干</v>
-      </c>
-      <c r="D64" t="str">
-        <v>biscuit(饼干)📢</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
-        <v>journey</v>
-      </c>
-      <c r="C65" t="str">
         <v>旅程</v>
-      </c>
-      <c r="D65" t="str">
-        <v>journey(旅程)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D65"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D58"/>
   </ignoredErrors>
 </worksheet>
 </file>